--- a/candidate_alocator/BaseDup.xlsx
+++ b/candidate_alocator/BaseDup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joaobresser/Documents/Pessoal/PS/candidate_allocation/candidate_alocator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF9D8D0-2811-A144-B43E-76513A338D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A54F42-A73E-E449-93C2-EC73C099CD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="180">
   <si>
     <t>TimeStamp</t>
   </si>
@@ -570,6 +570,12 @@
   </si>
   <si>
     <t>teste5@exemplo.com</t>
+  </si>
+  <si>
+    <t>teste4@al.insper.edu.br</t>
+  </si>
+  <si>
+    <t>teste4@exemplo.com</t>
   </si>
 </sst>
 </file>
@@ -1390,8 +1396,8 @@
       <c r="E2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>15</v>
+      <c r="F2" s="4">
+        <v>1</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>16</v>
@@ -1427,14 +1433,14 @@
         <v>11111111111</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" ref="D3:D6" si="0">D2-1</f>
+        <f t="shared" ref="D3:D7" si="0">D2-1</f>
         <v>999999998</v>
       </c>
       <c r="E3" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>24</v>
+      <c r="F3" s="4">
+        <v>2</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>25</v>
@@ -1476,8 +1482,8 @@
       <c r="E4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="24" t="s">
-        <v>15</v>
+      <c r="F4" s="24">
+        <v>3</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>32</v>
@@ -1519,8 +1525,8 @@
       <c r="E5" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="24" t="s">
-        <v>24</v>
+      <c r="F5" s="24">
+        <v>4</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>25</v>
@@ -1562,8 +1568,8 @@
       <c r="E6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="24" t="s">
-        <v>15</v>
+      <c r="F6" s="24">
+        <v>4</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>32</v>
@@ -1589,19 +1595,46 @@
       <c r="O6" s="4"/>
     </row>
     <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="5"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
+      <c r="A7" s="5">
+        <v>45819.80572916667</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="4">
+        <v>11111111115</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="0"/>
+        <v>999999994</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F7" s="24">
+        <v>5</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2310,20 +2343,19 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" xr:uid="{E0B0C37A-C9FB-DC42-B619-434A9D24BB1C}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{8AFFE448-B556-B048-A28F-007917B51F09}"/>
-    <hyperlink ref="E2" r:id="rId3" xr:uid="{B5E6254A-62D1-0549-82B0-7DCAB49D1267}"/>
-    <hyperlink ref="F6" r:id="rId4" xr:uid="{487901EF-4BBE-3F40-9FE4-F56BC0119AFA}"/>
-    <hyperlink ref="E5" r:id="rId5" xr:uid="{ADA865F5-8E4C-2148-B8DC-1D938BF5E8B3}"/>
-    <hyperlink ref="F5" r:id="rId6" xr:uid="{CF0A646C-AE01-E948-9069-F4A92BD22BA5}"/>
-    <hyperlink ref="H5" r:id="rId7" xr:uid="{FE457272-369B-D249-8AD2-E4EDB917F0D0}"/>
-    <hyperlink ref="H6" r:id="rId8" xr:uid="{686A0DC9-9583-2C47-8543-8E6BF82FF78F}"/>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{8AFFE448-B556-B048-A28F-007917B51F09}"/>
+    <hyperlink ref="E2" r:id="rId2" xr:uid="{B5E6254A-62D1-0549-82B0-7DCAB49D1267}"/>
+    <hyperlink ref="E5" r:id="rId3" xr:uid="{ADA865F5-8E4C-2148-B8DC-1D938BF5E8B3}"/>
+    <hyperlink ref="H5" r:id="rId4" xr:uid="{FE457272-369B-D249-8AD2-E4EDB917F0D0}"/>
+    <hyperlink ref="H6" r:id="rId5" xr:uid="{686A0DC9-9583-2C47-8543-8E6BF82FF78F}"/>
+    <hyperlink ref="H7" r:id="rId6" xr:uid="{01D71BDC-24B8-6343-A0D7-C94129F9C539}"/>
+    <hyperlink ref="E7" r:id="rId7" xr:uid="{FC79FC2B-DEC5-A44D-8712-EAB44BF503AC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="2">
+    <tablePart r:id="rId8"/>
     <tablePart r:id="rId9"/>
-    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>
